--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark, Sofia Åström</t>
+          <t>Sofia Åström, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofia Åström, Frédéric Forsmark</t>
+          <t>Frédéric Forsmark, Sofia Åström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>136483149</v>
       </c>
       <c r="B8" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark, Sofia Åström</t>
+          <t>Sofia Åström, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>136483149</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>136483149</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>136483149</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>136483149</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>136483149</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>136483149</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
